--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-types-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-types-medium.xlsx
@@ -460,19 +460,19 @@
         <v>System Testing do QA chạy để đảm bảo hệ thống xây đúng thiết kế kỹ thuật (SRS). Acceptance Testing do chính khách hàng/người dùng chạy để xác nhận hệ thống chạy đúng quy trình thực tế của họ và đem lại giá trị kinh doanh.</v>
       </c>
       <c r="F2" t="str">
-        <v>System: Kiểm thử toàn diện chức năng/phi chức năng dựa trên tài liệu SRS kỹ thuật; Acceptance: Kiểm thử dựa trên kịch bản nghiệp vụ thực tế của người dùng cuối để nghiệm thu — đặc tả kỹ thuật vs nghiệp vụ thực tế</v>
+        <v>System do khách hàng thực hiện; còn Acceptance do đội QA của dự án thực hiện — phân chia vai trò thực hiện</v>
       </c>
       <c r="G2" t="str">
-        <v>System do khách hàng thực hiện; còn Acceptance do đội QA của dự án thực hiện — phân chia vai trò thực hiện</v>
+        <v>System chỉ test trên môi trường Staging; còn Acceptance bắt buộc phải chạy thẳng trên Production — phân loại môi trường</v>
       </c>
       <c r="H2" t="str">
         <v>System bắt buộc phải chạy tự động; còn Acceptance bắt buộc phải test thủ công hoàn toàn — phân loại phương pháp test</v>
       </c>
       <c r="I2" t="str">
-        <v>System chỉ test trên môi trường Staging; còn Acceptance bắt buộc phải chạy thẳng trên Production — phân loại môi trường</v>
+        <v>System: Kiểm thử toàn diện chức năng/phi chức năng dựa trên tài liệu SRS kỹ thuật; Acceptance: Kiểm thử dựa trên kịch bản nghiệp vụ thực tế của người dùng cuối để nghiệm thu — đặc tả kỹ thuật vs nghiệp vụ thực tế</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Unit test yêu cầu test nhanh, độc lập. Nếu hàm A gọi Database thực tế, test case sẽ chạy chậm và phụ thuộc vào kết nối DB. Mocking tạo ra một đối tượng DB giả lập trả về kết quả định sẵn để kiểm tra đúng logic nội bộ của hàm A.</v>
       </c>
       <c r="F3" t="str">
-        <v>Cách ly đơn vị code đang kiểm thử (hàm A) khỏi các thành phần phụ thuộc bên ngoài chưa sẵn sàng (như Database, API bên ngoài) bằng cách dùng dữ liệu giả lập — cách ly đơn vị code cần test</v>
+        <v>Tạo ra các giao diện người dùng giả lập có hình vẽ hoạt hình để demo cho khách hàng — giao diện hoạt hình giả lập</v>
       </c>
       <c r="G3" t="str">
         <v>Tự động tăng tốc độ xử lý của vi xử lý máy chủ lên nhanh gấp đôi khi chạy test — tăng tốc độ máy chủ</v>
       </c>
       <c r="H3" t="str">
-        <v>Tạo ra các giao diện người dùng giả lập có hình vẽ hoạt hình để demo cho khách hàng — giao diện hoạt hình giả lập</v>
+        <v>Cách ly đơn vị code đang kiểm thử (hàm A) khỏi các thành phần phụ thuộc bên ngoài chưa sẵn sàng (như Database, API bên ngoài) bằng cách dùng dữ liệu giả lập — cách ly đơn vị code cần test</v>
       </c>
       <c r="I3" t="str">
         <v>Kiểm tra xem hệ thống có bị rò rỉ dữ liệu tài chính ra ngoài mạng internet hay không — kiểm thử rò rỉ dữ liệu</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>Load: Kiểm tra hệ thống dưới tải lượng người dùng bình thường dự kiến; Stress: Kiểm tra hệ thống dưới tải cực hạn vượt ngưỡng thiết kế để tìm điểm gãy (break point) của hệ thống — tải bình thường vs tải cực hạn tìm điểm gãy</v>
       </c>
       <c r="G4" t="str">
-        <v>Load chỉ dùng cho phần mềm điện thoại di động; còn Stress chỉ dùng cho phần mềm máy tính bàn — phân loại theo thiết bị</v>
+        <v>Load bắt buộc phải chạy ban ngày; còn Stress chỉ được phép chạy vào nửa đêm — giới hạn thời gian chạy test</v>
       </c>
       <c r="H4" t="str">
         <v>Load do lập trình viên tự test; còn Stress bắt buộc phải thuê chuyên gia tâm lý vào đánh giá — phân chia vai trò test</v>
       </c>
       <c r="I4" t="str">
-        <v>Load bắt buộc phải chạy ban ngày; còn Stress chỉ được phép chạy vào nửa đêm — giới hạn thời gian chạy test</v>
+        <v>Load chỉ dùng cho phần mềm điện thoại di động; còn Stress chỉ dùng cho phần mềm máy tính bàn — phân loại theo thiết bị</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Component Integration tích hợp các Class/Packages nội bộ trong code. SIT (System Integration Testing) là mức tích hợp cao hơn, kiểm tra xem ứng dụng của bạn có gọi API lấy dữ liệu và gửi nhận tin nhắn thành công với các hệ thống ERP, CRM, Cổng thanh toán của đối tác hay không.</v>
       </c>
       <c r="F6" t="str">
+        <v>SIT chỉ dùng cho các dự án chạy theo mô hình Waterfall; còn Component Integration chỉ dùng cho Agile — phân loại theo mô hình</v>
+      </c>
+      <c r="G6" t="str">
         <v>SIT kiểm tra giao tiếp giữa hệ thống đang phát triển với các hệ thống/ứng dụng bên ngoài khác; Component Integration kiểm tra giao tiếp giữa các module nội bộ bên trong một ứng dụng — tích hợp hệ thống ngoài vs tích hợp module nội bộ</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>SIT do khách hàng tự chạy thủ công; còn Component Integration do đội QA chạy tự động hoàn toàn — chủ thể thực hiện</v>
-      </c>
-      <c r="H6" t="str">
-        <v>SIT chỉ dùng cho các dự án chạy theo mô hình Waterfall; còn Component Integration chỉ dùng cho Agile — phân loại theo mô hình</v>
       </c>
       <c r="I6" t="str">
         <v>SIT bắt buộc phải chạy trên máy chủ Cloud AWS; còn Component Integration chỉ chạy được trên Google Cloud — nền tảng máy chủ</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Vì nó cho phép Tester tự do kiểm thử dựa trên kinh nghiệm, tư duy phản biện và khám phá hệ thống thời gian thực mà không bị gò bó bởi test case viết sẵn, giúp phát hiện các bug dị biệt — kiểm thử tự do khám phá phát hiện bug ẩn</v>
       </c>
       <c r="G7" t="str">
+        <v>Vì nó bắt buộc Tester phải chạy kiểm thử trên điện thoại di động khi đang di chuyển ngoài đường — kiểm thử di động</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Vì nó loại bỏ hoàn toàn việc phải báo cáo lỗi lên các hệ thống quản lý bug như Jira — loại bỏ báo cáo lỗi</v>
+      </c>
+      <c r="I7" t="str">
         <v>Vì nó tự động hóa 100% việc viết mã nguồn test case bằng trí tuệ nhân tạo AI — tự động viết test case</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Vì nó bắt buộc Tester phải chạy kiểm thử trên điện thoại di động khi đang di chuyển ngoài đường — kiểm thử di động</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Vì nó loại bỏ hoàn toàn việc phải báo cáo lỗi lên các hệ thống quản lý bug như Jira — loại bỏ báo cáo lỗi</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>Compatibility Testing đảm bảo ứng dụng hiển thị và hoạt động đúng chuẩn trên cả Chrome, Safari, Firefox; trên iOS và Android; trên màn hình nhỏ điện thoại đến màn hình to máy tính.</v>
       </c>
       <c r="F8" t="str">
-        <v>Khả năng phần mềm chạy ổn định và hiển thị đúng trên các cấu hình hệ điều hành, trình duyệt, kích thước màn hình và thiết bị phần cứng khác nhau — tính tương thích đa nền tảng</v>
+        <v>Khả năng kết nối cơ sở dữ liệu quan hệ của hệ thống với hệ quản trị cơ sở dữ liệu NoSQL — tương thích cơ sở dữ liệu</v>
       </c>
       <c r="G8" t="str">
-        <v>Khả năng kết nối cơ sở dữ liệu quan hệ của hệ thống với hệ quản trị cơ sở dữ liệu NoSQL — tương thích cơ sở dữ liệu</v>
+        <v>Khả năng phần mềm tự động nâng cấp phiên bản mới mà không cần người dùng nhấn nút đồng ý — tự động nâng cấp</v>
       </c>
       <c r="H8" t="str">
         <v>Mức độ tương hợp về tính cách giữa lập trình viên và kiểm thử viên trong team — tương hợp nhân sự</v>
       </c>
       <c r="I8" t="str">
-        <v>Khả năng phần mềm tự động nâng cấp phiên bản mới mà không cần người dùng nhấn nút đồng ý — tự động nâng cấp</v>
+        <v>Khả năng phần mềm chạy ổn định và hiển thị đúng trên các cấu hình hệ điều hành, trình duyệt, kích thước màn hình và thiết bị phần cứng khác nhau — tính tương thích đa nền tảng</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -690,10 +690,10 @@
         <v>Vulnerability Scanning do QA tự chạy; còn Penetration Testing do hacker mũ đen tự ý thực hiện bất hợp pháp — tính pháp lý</v>
       </c>
       <c r="H9" t="str">
+        <v>Vulnerability Scanning bắt buộc phải chạy hàng ngày; còn Penetration Testing chỉ chạy 10 năm một lần — giới hạn tần suất chạy</v>
+      </c>
+      <c r="I9" t="str">
         <v>Vulnerability Scanning chỉ áp dụng cho mã nguồn Backend; còn Penetration Testing chỉ áp dụng cho giao diện Frontend — phân loại layer test</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Vulnerability Scanning bắt buộc phải chạy hàng ngày; còn Penetration Testing chỉ chạy 10 năm một lần — giới hạn tần suất chạy</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Nghịch lý thuốc trừ sâu chỉ ra rằng nếu dùng mãi 1 loại thuốc, sâu sẽ kháng thuốc (chạy đi chạy lại 1 bộ test case, hệ thống sẽ hết lỗi phát hiện thêm). QA phải liên tục cập nhật bộ test hồi quy để bao phủ các kịch bản mới phát sinh.</v>
       </c>
       <c r="F10" t="str">
+        <v>Tăng gấp đôi tần suất chạy bộ test hồi quy hiện tại lên 2 lần một ngày — tăng tần suất chạy</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Yêu cầu lập trình viên viết code bằng một ngôn ngữ lập trình khác sau mỗi sprint — thay đổi ngôn ngữ code</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Sử dụng các công cụ tự động hóa để chạy ngẫu nhiên các câu lệnh SQL vào database — chạy SQL ngẫu nhiên</v>
+      </c>
+      <c r="I10" t="str">
         <v>Thường xuyên cập nhật, bổ sung các kịch bản test mới và loại bỏ các test case đã lỗi thời khỏi bộ test hồi quy — làm mới bộ test case</v>
       </c>
-      <c r="G10" t="str">
-        <v>Tăng gấp đôi tần suất chạy bộ test hồi quy hiện tại lên 2 lần một ngày — tăng tần suất chạy</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Yêu cầu lập trình viên viết code bằng một ngôn ngữ lập trình khác sau mỗi sprint — thay đổi ngôn ngữ code</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Sử dụng các công cụ tự động hóa để chạy ngẫu nhiên các câu lệnh SQL vào database — chạy SQL ngẫu nhiên</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -754,10 +754,10 @@
         <v>Alpha Testing chỉ test trên máy tính chạy Windows; còn Beta Testing chỉ test trên máy chạy macOS — hệ điều hành chạy test</v>
       </c>
       <c r="H11" t="str">
+        <v>Alpha Testing do dev tự viết code test; còn Beta Testing do AI tự động chạy kiểm thử — phương pháp thực hiện</v>
+      </c>
+      <c r="I11" t="str">
         <v>Alpha Testing hoàn toàn bảo mật; còn Beta Testing bắt buộc phải công khai toàn bộ mã nguồn ra internet — tính bảo mật mã nguồn</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Alpha Testing do dev tự viết code test; còn Beta Testing do AI tự động chạy kiểm thử — phương pháp thực hiện</v>
       </c>
       <c r="J11">
         <v>1</v>
